--- a/data/Summary_Table.xlsx
+++ b/data/Summary_Table.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Danel\Documents\STADVDB\H01 - Query Processing\STADVDB-HO1-main\STADVDB-HO1-main\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{96C8CD4C-D1A0-4F47-9114-794693BBE1A2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F8582210-545D-441B-B63E-47DE78035ABE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Part C Summary" sheetId="1" r:id="rId1"/>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="43" uniqueCount="41">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="34">
   <si>
     <t>Query</t>
   </si>
@@ -55,16 +55,7 @@
     <t>Indexing + Reformulating Subqueries</t>
   </si>
   <si>
-    <t>1.953 s</t>
-  </si>
-  <si>
-    <t>0.093 s</t>
-  </si>
-  <si>
-    <t>58,574.15</t>
-  </si>
-  <si>
-    <t>3,405,002.50*</t>
+    <t>Three-table row-level join replaced by a single pre-aggregated derived table on payment. The rental join is removed entirely: COUNT(DISTINCT p.rental_id) reproduces the baseline's rental count exactly. Covering index idx_payment_customer_rental_amount lets the whole aggregate run as a covering index scan, so the payment table itself is never read. The join to customer becomes a 10-row primary-key lookup because LIMIT is applied before that join.</t>
   </si>
   <si>
     <t>Q2</t>
@@ -73,89 +64,80 @@
     <t>Reformulating Subqueries</t>
   </si>
   <si>
-    <t>2.078 s</t>
-  </si>
-  <si>
-    <t>0.187 s</t>
-  </si>
-  <si>
-    <t>5,994.66</t>
-  </si>
-  <si>
-    <t>339,289.38*</t>
+    <t>Same pre-aggregation as Q1, with HAVING COUNT(*) &gt;= 30 pushed inside the derived table so 257 of 1,500 customers are discarded before the join instead of after. AVG(amount) is computed inside the subquery to match the baseline's rounding exactly. customer.active is left unindexed on purpose since 95% of rows are active, so an index there is not selective.</t>
   </si>
   <si>
     <t>Q3</t>
   </si>
   <si>
-    <t>3.063 s</t>
-  </si>
-  <si>
-    <t>~0 s</t>
-  </si>
-  <si>
-    <t>90,386.87</t>
-  </si>
-  <si>
-    <t>1.45</t>
+    <t>Denormalization</t>
+  </si>
+  <si>
+    <t>Monthly rollup precomputed once into store_month_revenue, keyed on (store_id, rental_month). The report becomes a 12-row primary-key index scan with no join, no aggregation and no filesort, since the clustered index already matches the required ORDER BY. Trade-off: the table is redundant data and goes stale on every new rental or payment.</t>
   </si>
   <si>
     <t>Q4</t>
   </si>
   <si>
-    <t>1.1813 s</t>
-  </si>
-  <si>
-    <t>0.109 s</t>
-  </si>
-  <si>
-    <t>3,390,670.75*</t>
-  </si>
-  <si>
-    <t>Methodology Notes</t>
-  </si>
-  <si>
-    <t>Execution time: median of several runs of the plain SELECT statement, from MySQL Workbench's reported Duration (not Fetch time).</t>
-  </si>
-  <si>
-    <t>Estimated cost: the 'query_cost' value from EXPLAIN FORMAT=JSON.</t>
-  </si>
-  <si>
-    <t>On EXPLAIN ANALYZE and the inflated cost figures (Q1, Q2, Q4):</t>
-  </si>
-  <si>
-    <t>MySQL's optimizer keeps no real statistics on derived tables built from a GROUP BY subquery, since they are temporary and only exist at query time. When costing the outer join, it falls back to assuming worst-case row counts for these derived tables — as if no aggregation had happened at all — which makes EXPLAIN FORMAT=JSON report a much higher cost for the optimized queries than the baseline, even though they run several times faster in practice.</t>
-  </si>
-  <si>
-    <t>EXPLAIN ANALYZE was run for each affected query to check this. Unlike EXPLAIN FORMAT=JSON, EXPLAIN ANALYZE actually executes the query and reports real row counts and real timings per operation. It confirmed the derived tables genuinely materialize to their expected small size (~1,500 rows, one per customer) rather than the inflated estimate — so the discrepancy is a limitation of the optimizer's static cost model, not a real regression. Real execution time is therefore used as the primary metric throughout; the cost figure is reported alongside for completeness.</t>
-  </si>
-  <si>
-    <t>Data volume at time of measurement (matches Part B): customer = 1,500 rows; rental = 119,801 rows; payment = 120,000 rows.</t>
-  </si>
-  <si>
-    <t>Summary Table</t>
-  </si>
-  <si>
-    <t>Row-level 3-table join replaced with pre-aggregated derived tables (payment, rental grouped to customer level) and covering index payment(customer_id, amount) allowing retrieval from this index structure instead of scanning the table. EXPLAIN ANALYZE confirmed real join only touches 10 rows (LIMIT pushed before the join).</t>
-  </si>
-  <si>
-    <t>Same pre-aggregation as Q1, plus HAVING COUNT(*) &gt;= 10 pushed into the rental subquery. EXPLAIN ANALYZE showed this filter barely excludes anyone at this data volume and most of the gain is from avoiding fan-out, not the filter itself.</t>
-  </si>
-  <si>
-    <t>Same pre-aggregation fix as Q1/Q2, confirmed by EXPLAIN ANALYZE (1,500 rows per aggregate, collapsing to 2 final rows).</t>
-  </si>
-  <si>
-    <t>Denormalization</t>
-  </si>
-  <si>
-    <t>Replaced with a full rollup table store_month_revenue making query now reads 12 precomputed rows via a primary-key scan.</t>
+    <t>Two chained LEFT JOINs that fanned out to one row per payment replaced by two independently pre-aggregated derived tables, one per customer each, so the outer GROUP BY sees 1,500 rows instead of ~120,000. Both aggregates run as covering index scans. COUNT(*) is safe in place of COUNT(DISTINCT customer_id) since neither derived table can duplicate a customer row.</t>
+  </si>
+  <si>
+    <t>The index: idx_payment_customer_rental_amount (customer_id, rental_id, amount)</t>
+  </si>
+  <si>
+    <t>SUMMARY TABLE</t>
+  </si>
+  <si>
+    <t>Cost figures in red (Q1, Q4) are not comparable to the baseline. In the Notes sheet, check 'Optimized cost looks worse' section. Execution time is the primary metric.</t>
+  </si>
+  <si>
+    <t>Optimized cost looks worse (Q1 and Q4)</t>
+  </si>
+  <si>
+    <t>&gt; Q2 and Q3 do improve on cost as well (27,773 to 4,353; 81,588 to 1.45), which shows the effect is a quirk of derived-table costing, not a pattern across the board.</t>
+  </si>
+  <si>
+    <t>&gt; Conclusion: a cost estimate is a static guess, not a measurement. Real execution time is the metric, and EXPLAIN ANALYZE is what settles the argument.</t>
+  </si>
+  <si>
+    <t>&gt; Q1's cost barely moves (55,375 to 55,503) yet the query runs about 8 times faster, for the same reason.</t>
+  </si>
+  <si>
+    <t>&gt; Q4 is the extreme case: the estimate is 3.06 billion rows, the reality is 1,500. EXPLAIN ANALYZE proves the derived tables materialise to 1,500 rows each.</t>
+  </si>
+  <si>
+    <t>&gt; MySQL keeps no statistics on a derived table built from GROUP BY, because it only exists during the query. When costing the outer join it assumes the worst case, as if no aggregation had happened.</t>
+  </si>
+  <si>
+    <t>NOTES</t>
+  </si>
+  <si>
+    <t>Techniques used</t>
+  </si>
+  <si>
+    <t>&gt;  Creating and Using Indexes: one covering index on payment, used by Q1, Q2 and Q4.</t>
+  </si>
+  <si>
+    <t>&gt;  Denormalization: the store_month_revenue summary table for Q3.</t>
+  </si>
+  <si>
+    <t>&gt;  Reformulating Subqueries: the derived-table rewrites in Q1, Q2 and Q4.</t>
+  </si>
+  <si>
+    <t>&gt;  Q1, Q2 and Q4 read only these three columns from payment, so the index answers them on its own. EXPLAIN shows Using index, and EXPLAIN ANALYZE shows a covering index scan. The payment table is never touched.</t>
+  </si>
+  <si>
+    <t>&gt;  Column order matters: customer_id comes first because it is what the GROUP BY needs. An index on (amount, customer_id) would be useless here.</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="6" x14ac:knownFonts="1">
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="0.000"/>
+  </numFmts>
+  <fonts count="10" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -170,26 +152,52 @@
     </font>
     <font>
       <b/>
-      <sz val="14"/>
+      <sz val="13"/>
       <name val="Arial"/>
       <family val="2"/>
     </font>
     <font>
       <i/>
       <sz val="9"/>
-      <color rgb="FF666666"/>
+      <color rgb="FF595959"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FFC00000"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="9"/>
+      <color rgb="FFC00000"/>
       <name val="Arial"/>
       <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="Arial"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="10"/>
+      <color rgb="FF1F3864"/>
       <name val="Arial"/>
       <family val="2"/>
     </font>
@@ -203,8 +211,8 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF2F5597"/>
-        <bgColor rgb="FF0066CC"/>
+        <fgColor rgb="FF1F3864"/>
+        <bgColor rgb="FF333333"/>
       </patternFill>
     </fill>
   </fills>
@@ -218,16 +226,16 @@
     </border>
     <border>
       <left style="thin">
-        <color rgb="FFB7B7B7"/>
+        <color rgb="FFBFBFBF"/>
       </left>
       <right style="thin">
-        <color rgb="FFB7B7B7"/>
+        <color rgb="FFBFBFBF"/>
       </right>
       <top style="thin">
-        <color rgb="FFB7B7B7"/>
+        <color rgb="FFBFBFBF"/>
       </top>
       <bottom style="thin">
-        <color rgb="FFB7B7B7"/>
+        <color rgb="FFBFBFBF"/>
       </bottom>
       <diagonal/>
     </border>
@@ -235,28 +243,35 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
+      <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="4" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="4" fontId="7" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -268,7 +283,7 @@
     <indexedColors>
       <rgbColor rgb="FF000000"/>
       <rgbColor rgb="FFFFFFFF"/>
-      <rgbColor rgb="FFFF0000"/>
+      <rgbColor rgb="FFC00000"/>
       <rgbColor rgb="FF00FF00"/>
       <rgbColor rgb="FF0000FF"/>
       <rgbColor rgb="FFFFFF00"/>
@@ -280,7 +295,7 @@
       <rgbColor rgb="FF808000"/>
       <rgbColor rgb="FF800080"/>
       <rgbColor rgb="FF008080"/>
-      <rgbColor rgb="FFB7B7B7"/>
+      <rgbColor rgb="FFBFBFBF"/>
       <rgbColor rgb="FF808080"/>
       <rgbColor rgb="FF9999FF"/>
       <rgbColor rgb="FF993366"/>
@@ -312,15 +327,15 @@
       <rgbColor rgb="FFFFCC00"/>
       <rgbColor rgb="FFFF9900"/>
       <rgbColor rgb="FFFF6600"/>
-      <rgbColor rgb="FF666666"/>
+      <rgbColor rgb="FF595959"/>
       <rgbColor rgb="FF969696"/>
-      <rgbColor rgb="FF003366"/>
+      <rgbColor rgb="FF1F3864"/>
       <rgbColor rgb="FF339966"/>
       <rgbColor rgb="FF003300"/>
       <rgbColor rgb="FF333300"/>
       <rgbColor rgb="FF993300"/>
       <rgbColor rgb="FF993366"/>
-      <rgbColor rgb="FF2F5597"/>
+      <rgbColor rgb="FF333399"/>
       <rgbColor rgb="FF333333"/>
       <rgbColor rgb="00003366"/>
       <rgbColor rgb="00339966"/>
@@ -522,167 +537,148 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G10"/>
+  <dimension ref="A1:G11"/>
   <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="8" customWidth="1"/>
-    <col min="2" max="2" width="30" customWidth="1"/>
-    <col min="3" max="5" width="16" customWidth="1"/>
-    <col min="6" max="6" width="18" customWidth="1"/>
-    <col min="7" max="7" width="52" customWidth="1"/>
+    <col min="1" max="1" width="7" customWidth="1"/>
+    <col min="2" max="2" width="26" customWidth="1"/>
+    <col min="3" max="4" width="15" customWidth="1"/>
+    <col min="5" max="6" width="16" customWidth="1"/>
+    <col min="7" max="7" width="70" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="17.399999999999999" x14ac:dyDescent="0.3">
-      <c r="A1" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="B1" s="3"/>
-      <c r="C1" s="3"/>
-      <c r="D1" s="3"/>
-      <c r="E1" s="3"/>
-      <c r="F1" s="3"/>
-      <c r="G1" s="3"/>
+    <row r="1" spans="1:7" ht="16.8" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
+        <v>19</v>
+      </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A2" s="2"/>
-      <c r="B2" s="2"/>
-      <c r="C2" s="2"/>
-      <c r="D2" s="2"/>
-      <c r="E2" s="2"/>
-      <c r="F2" s="2"/>
-      <c r="G2" s="2"/>
-    </row>
-    <row r="4" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="5" t="s">
+    </row>
+    <row r="4" spans="1:7" ht="31.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B4" s="5" t="s">
+      <c r="B4" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="C4" s="5" t="s">
+      <c r="C4" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D4" s="5" t="s">
+      <c r="D4" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E4" s="5" t="s">
+      <c r="E4" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="F4" s="5" t="s">
+      <c r="F4" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G4" s="5" t="s">
+      <c r="G4" s="3" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="5" spans="1:7" ht="87" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="6" t="s">
+    <row r="5" spans="1:7" ht="105" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="B5" s="6" t="s">
+      <c r="B5" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="C5" s="7" t="s">
+      <c r="C5" s="6">
+        <v>0.77342999999999995</v>
+      </c>
+      <c r="D5" s="6">
+        <v>9.4E-2</v>
+      </c>
+      <c r="E5" s="7">
+        <v>55375</v>
+      </c>
+      <c r="F5" s="8">
+        <v>55502.5</v>
+      </c>
+      <c r="G5" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="D5" s="7" t="s">
+    </row>
+    <row r="6" spans="1:7" ht="105" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="E5" s="7" t="s">
+      <c r="B6" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="F5" s="7" t="s">
+      <c r="C6" s="6">
+        <v>0.77686599999999995</v>
+      </c>
+      <c r="D6" s="6">
+        <v>9.4E-2</v>
+      </c>
+      <c r="E6" s="7">
+        <v>27773</v>
+      </c>
+      <c r="F6" s="7">
+        <v>4352.5</v>
+      </c>
+      <c r="G6" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="G5" s="9" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7" ht="75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="6" t="s">
+    </row>
+    <row r="7" spans="1:7" ht="105" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A7" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="B6" s="6" t="s">
+      <c r="B7" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="C6" s="7" t="s">
+      <c r="C7" s="6">
+        <v>1.2913840000000001</v>
+      </c>
+      <c r="D7" s="6">
+        <v>1.4999999999999999E-2</v>
+      </c>
+      <c r="E7" s="7">
+        <v>81588</v>
+      </c>
+      <c r="F7" s="7">
+        <v>1.45</v>
+      </c>
+      <c r="G7" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="D6" s="7" t="s">
+    </row>
+    <row r="8" spans="1:7" ht="105" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="E6" s="7" t="s">
+      <c r="B8" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C8" s="6">
+        <v>0.83129200000000003</v>
+      </c>
+      <c r="D8" s="6">
+        <v>0.109</v>
+      </c>
+      <c r="E8" s="7">
+        <v>81890</v>
+      </c>
+      <c r="F8" s="8">
+        <v>3390670.75</v>
+      </c>
+      <c r="G8" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="F6" s="7" t="s">
-        <v>18</v>
-      </c>
-      <c r="G6" s="9" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7" ht="75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="B7" s="9" t="s">
-        <v>39</v>
-      </c>
-      <c r="C7" s="7" t="s">
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A10" s="9" t="s">
         <v>20</v>
       </c>
-      <c r="D7" s="7" t="s">
-        <v>21</v>
-      </c>
-      <c r="E7" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="F7" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="G7" s="9" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7" ht="75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="B8" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="C8" s="7" t="s">
-        <v>25</v>
-      </c>
-      <c r="D8" s="7" t="s">
-        <v>26</v>
-      </c>
-      <c r="E8" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="F8" s="7" t="s">
-        <v>27</v>
-      </c>
-      <c r="G8" s="9" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7" ht="14.4" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="10" spans="1:7" ht="13.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="1"/>
-      <c r="B10" s="1"/>
-      <c r="C10" s="1"/>
-      <c r="D10" s="1"/>
-      <c r="E10" s="1"/>
-      <c r="F10" s="1"/>
-      <c r="G10" s="1"/>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A11" s="2"/>
     </row>
   </sheetData>
-  <mergeCells count="3">
-    <mergeCell ref="A1:G1"/>
-    <mergeCell ref="A2:G2"/>
-    <mergeCell ref="A10:G10"/>
-  </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
 </worksheet>
@@ -690,62 +686,140 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:A12"/>
+  <dimension ref="A1:A49"/>
   <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="110" customWidth="1"/>
+    <col min="1" max="1" width="135" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" ht="17.399999999999999" x14ac:dyDescent="0.3">
-      <c r="A1" s="4" t="s">
+    <row r="1" spans="1:1" ht="16.8" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A3" s="10" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="2" spans="1:1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="8"/>
-    </row>
-    <row r="3" spans="1:1" ht="45" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="8" t="s">
+    <row r="4" spans="1:1" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="12" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="4" spans="1:1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="8"/>
-    </row>
-    <row r="5" spans="1:1" ht="45" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="8" t="s">
+    <row r="5" spans="1:1" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="12" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="6" spans="1:1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="8"/>
-    </row>
-    <row r="7" spans="1:1" ht="45" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="8" t="s">
+    <row r="6" spans="1:1" ht="12.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="12" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="8" spans="1:1" ht="45" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="8" t="s">
+    <row r="7" spans="1:1" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="8" spans="1:1" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="10" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="9" spans="1:1" ht="26.4" x14ac:dyDescent="0.3">
+      <c r="A9" s="12" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="9" spans="1:1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="8"/>
-    </row>
-    <row r="10" spans="1:1" ht="45" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="8" t="s">
+    <row r="10" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A10" s="12" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="11" spans="1:1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="8"/>
-    </row>
-    <row r="12" spans="1:1" ht="45" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="8" t="s">
-        <v>34</v>
-      </c>
-    </row>
+    <row r="11" spans="1:1" ht="14.4" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="12" spans="1:1" ht="25.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="10" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="13" spans="1:1" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A13" s="12" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="14" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A14" s="12" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="15" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A15" s="12" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="16" spans="1:1" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A16" s="12" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="17" spans="1:1" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A17" s="12" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="18" spans="1:1" ht="13.5" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="19" spans="1:1" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A19" s="10"/>
+    </row>
+    <row r="20" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A20" s="12"/>
+    </row>
+    <row r="21" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A21" s="11"/>
+    </row>
+    <row r="22" spans="1:1" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A22" s="11"/>
+    </row>
+    <row r="23" spans="1:1" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="24" spans="1:1" ht="13.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A24" s="10"/>
+    </row>
+    <row r="25" spans="1:1" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A25" s="11"/>
+    </row>
+    <row r="26" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A26" s="11"/>
+    </row>
+    <row r="27" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A27" s="11"/>
+    </row>
+    <row r="28" spans="1:1" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A28" s="11"/>
+    </row>
+    <row r="29" spans="1:1" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="30" spans="1:1" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A30" s="10"/>
+    </row>
+    <row r="31" spans="1:1" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A31" s="11"/>
+    </row>
+    <row r="32" spans="1:1" ht="13.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A32" s="11"/>
+    </row>
+    <row r="33" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A33" s="11"/>
+    </row>
+    <row r="34" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A34" s="11"/>
+    </row>
+    <row r="35" spans="1:1" ht="13.8" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="36" spans="1:1" ht="14.4" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="37" spans="1:1" ht="16.8" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="40" spans="1:1" ht="16.2" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="41" spans="1:1" ht="15.6" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="42" spans="1:1" ht="14.4" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="43" spans="1:1" ht="14.4" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="46" spans="1:1" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="47" spans="1:1" ht="16.2" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="48" spans="1:1" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="49" ht="15.6" customHeight="1" x14ac:dyDescent="0.3"/>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>

--- a/data/Summary_Table.xlsx
+++ b/data/Summary_Table.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Danel\Documents\STADVDB\H01 - Query Processing\STADVDB-HO1-main\STADVDB-HO1-main\data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\USER\Desktop\DLSU Stuff\STADVDB\sakila-db\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F8582210-545D-441B-B63E-47DE78035ABE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2A88A436-4A7C-4BE5-825E-DA47C5828048}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="5670" yWindow="3660" windowWidth="28695" windowHeight="15345" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Part C Summary" sheetId="1" r:id="rId1"/>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="34">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="35">
   <si>
     <t>Query</t>
   </si>
@@ -64,9 +64,6 @@
     <t>Reformulating Subqueries</t>
   </si>
   <si>
-    <t>Same pre-aggregation as Q1, with HAVING COUNT(*) &gt;= 30 pushed inside the derived table so 257 of 1,500 customers are discarded before the join instead of after. AVG(amount) is computed inside the subquery to match the baseline's rounding exactly. customer.active is left unindexed on purpose since 95% of rows are active, so an index there is not selective.</t>
-  </si>
-  <si>
     <t>Q3</t>
   </si>
   <si>
@@ -94,9 +91,6 @@
     <t>Optimized cost looks worse (Q1 and Q4)</t>
   </si>
   <si>
-    <t>&gt; Q2 and Q3 do improve on cost as well (27,773 to 4,353; 81,588 to 1.45), which shows the effect is a quirk of derived-table costing, not a pattern across the board.</t>
-  </si>
-  <si>
     <t>&gt; Conclusion: a cost estimate is a static guess, not a measurement. Real execution time is the metric, and EXPLAIN ANALYZE is what settles the argument.</t>
   </si>
   <si>
@@ -128,6 +122,15 @@
   </si>
   <si>
     <t>&gt;  Column order matters: customer_id comes first because it is what the GROUP BY needs. An index on (amount, customer_id) would be useless here.</t>
+  </si>
+  <si>
+    <t>Reformulating Subqueries / Pre-aggregation</t>
+  </si>
+  <si>
+    <t>&gt; Q2 and Q3 do improve on cost as well (5,525.76 to 2,178.18; 81,588 to 1.45), which shows the effect is a quirk of derived-table costing, not a pattern across the board.</t>
+  </si>
+  <si>
+    <t>The correlated DEPENDENT SUBQUERY on rental is eliminated. Instead, the optimized query pre-aggregates rental and payment by customer_id in a derived table, performs the GROUP BY once, and then joins the aggregated results to customer. This reduces the repeated rental lookup performed for each customer in the baseline query.</t>
   </si>
 </sst>
 </file>
@@ -243,7 +246,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -271,6 +274,9 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -538,7 +544,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:G11"/>
-  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="7" customWidth="1"/>
     <col min="2" max="2" width="26" customWidth="1"/>
@@ -547,15 +553,15 @@
     <col min="7" max="7" width="70" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="16.8" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" s="2"/>
     </row>
-    <row r="4" spans="1:7" ht="31.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:7" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
         <v>0</v>
       </c>
@@ -578,11 +584,11 @@
         <v>6</v>
       </c>
     </row>
-    <row r="5" spans="1:7" ht="105" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:7" ht="105" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="B5" s="5" t="s">
+      <c r="B5" s="13" t="s">
         <v>8</v>
       </c>
       <c r="C5" s="6">
@@ -597,39 +603,39 @@
       <c r="F5" s="8">
         <v>55502.5</v>
       </c>
-      <c r="G5" s="5" t="s">
+      <c r="G5" s="13" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="6" spans="1:7" ht="105" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:7" ht="105" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="B6" s="5" t="s">
-        <v>11</v>
+      <c r="B6" s="13" t="s">
+        <v>32</v>
       </c>
       <c r="C6" s="6">
-        <v>0.77686599999999995</v>
+        <v>0.32800000000000001</v>
       </c>
       <c r="D6" s="6">
-        <v>9.4E-2</v>
+        <v>0.313</v>
       </c>
       <c r="E6" s="7">
-        <v>27773</v>
+        <v>5525.76</v>
       </c>
       <c r="F6" s="7">
-        <v>4352.5</v>
-      </c>
-      <c r="G6" s="5" t="s">
+        <v>2178.1799999999998</v>
+      </c>
+      <c r="G6" s="13" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" ht="105" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="4" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="7" spans="1:7" ht="105" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="4" t="s">
+      <c r="B7" s="5" t="s">
         <v>13</v>
-      </c>
-      <c r="B7" s="5" t="s">
-        <v>14</v>
       </c>
       <c r="C7" s="6">
         <v>1.2913840000000001</v>
@@ -644,12 +650,12 @@
         <v>1.45</v>
       </c>
       <c r="G7" s="5" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" ht="105" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="4" t="s">
         <v>15</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7" ht="105" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="4" t="s">
-        <v>16</v>
       </c>
       <c r="B8" s="5" t="s">
         <v>11</v>
@@ -667,15 +673,15 @@
         <v>3390670.75</v>
       </c>
       <c r="G8" s="5" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10" s="9" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A11" s="2"/>
     </row>
   </sheetData>
@@ -687,139 +693,139 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:A49"/>
-  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="135" customWidth="1"/>
+    <col min="1" max="1" width="139.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" ht="16.8" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:1" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A3" s="10" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="4" spans="1:1" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="12" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A3" s="10" t="s">
+    <row r="5" spans="1:1" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="12" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="4" spans="1:1" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="12" t="s">
+    <row r="6" spans="1:1" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="12" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="5" spans="1:1" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="12" t="s">
+    <row r="7" spans="1:1" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="8" spans="1:1" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="10" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="9" spans="1:1" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="A9" s="12" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="6" spans="1:1" ht="12.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="12" t="s">
+    <row r="10" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A10" s="12" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="7" spans="1:1" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="8" spans="1:1" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="10" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="9" spans="1:1" ht="26.4" x14ac:dyDescent="0.3">
-      <c r="A9" s="12" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="10" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A10" s="12" t="s">
+    <row r="11" spans="1:1" ht="14.45" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="12" spans="1:1" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="10" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="13" spans="1:1" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="12" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="14" spans="1:1" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="A14" s="12" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="15" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A15" s="12" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="16" spans="1:1" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="12" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="11" spans="1:1" ht="14.4" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="12" spans="1:1" ht="25.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="10" t="s">
+    <row r="17" spans="1:1" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="12" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="13" spans="1:1" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="12" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="14" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A14" s="12" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="15" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A15" s="12" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="16" spans="1:1" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="12" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="17" spans="1:1" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="12" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="18" spans="1:1" ht="13.5" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="19" spans="1:1" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:1" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="19" spans="1:1" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="10"/>
     </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A20" s="12"/>
     </row>
-    <row r="21" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A21" s="11"/>
     </row>
-    <row r="22" spans="1:1" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:1" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="11"/>
     </row>
-    <row r="23" spans="1:1" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="24" spans="1:1" ht="13.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:1" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="24" spans="1:1" ht="13.15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="10"/>
     </row>
-    <row r="25" spans="1:1" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:1" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="11"/>
     </row>
-    <row r="26" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A26" s="11"/>
     </row>
-    <row r="27" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A27" s="11"/>
     </row>
-    <row r="28" spans="1:1" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:1" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="11"/>
     </row>
-    <row r="29" spans="1:1" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="30" spans="1:1" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:1" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="30" spans="1:1" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="10"/>
     </row>
-    <row r="31" spans="1:1" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:1" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="11"/>
     </row>
-    <row r="32" spans="1:1" ht="13.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:1" ht="13.15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="11"/>
     </row>
-    <row r="33" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A33" s="11"/>
     </row>
-    <row r="34" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A34" s="11"/>
     </row>
-    <row r="35" spans="1:1" ht="13.8" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="36" spans="1:1" ht="14.4" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="37" spans="1:1" ht="16.8" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="40" spans="1:1" ht="16.2" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="41" spans="1:1" ht="15.6" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="42" spans="1:1" ht="14.4" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="43" spans="1:1" ht="14.4" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="46" spans="1:1" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="47" spans="1:1" ht="16.2" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="48" spans="1:1" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="49" ht="15.6" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="35" spans="1:1" ht="13.9" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="36" spans="1:1" ht="14.45" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="37" spans="1:1" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="40" spans="1:1" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="41" spans="1:1" ht="15.6" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="42" spans="1:1" ht="14.45" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="43" spans="1:1" ht="14.45" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="46" spans="1:1" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="47" spans="1:1" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="48" spans="1:1" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="49" ht="15.6" customHeight="1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
